--- a/artfynd/A 60449-2022 artfynd.xlsx
+++ b/artfynd/A 60449-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111992846</v>
+        <v>136125881</v>
       </c>
       <c r="B2" t="n">
-        <v>93197</v>
+        <v>92336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,48 +691,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åsryggen, Lindsbergsmyrabäcken, Hls</t>
+          <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534883</v>
+        <v>534841</v>
       </c>
       <c r="R2" t="n">
-        <v>6830246</v>
+        <v>6830296</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,70 +780,65 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111992846</t>
+          <t>https://artportalen.se/Sighting/136125881</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117718209</v>
+        <v>111992846</v>
       </c>
       <c r="B3" t="n">
-        <v>99035</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bläckhornsvägen, korsningen, Hls</t>
+          <t>Åsryggen, Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534584</v>
+        <v>534883</v>
       </c>
       <c r="R3" t="n">
-        <v>6830523</v>
+        <v>6830246</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,12 +862,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,16 +904,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117718209</t>
+          <t>https://artportalen.se/Sighting/111992846</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117718013</v>
+        <v>117718209</v>
       </c>
       <c r="B4" t="n">
-        <v>99153</v>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,26 +921,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -961,7 +948,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -976,7 +967,7 @@
         <v>6830523</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,11 +997,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>45 blommor.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,13 +1023,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117718013</t>
+          <t>https://artportalen.se/Sighting/117718209</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118405116</v>
+        <v>117718013</v>
       </c>
       <c r="B5" t="n">
         <v>99153</v>
@@ -1073,7 +1059,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>91</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1081,23 +1067,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Övre Bursjövägen, Lindsbergsmyrsbäcken, Hls</t>
+          <t>Bläckhornsvägen, korsningen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534562</v>
+        <v>534584</v>
       </c>
       <c r="R5" t="n">
-        <v>6830447</v>
+        <v>6830523</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1124,12 +1106,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>45 blommor.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,6 +1142,125 @@
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117718013</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118405116</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Övre Bursjövägen, Lindsbergsmyrsbäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>534562</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6830447</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/118405116</t>
         </is>
@@ -1166,6 +1272,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60449-2022 artfynd.xlsx
+++ b/artfynd/A 60449-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136125881</v>
       </c>
       <c r="B2" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60449-2022 artfynd.xlsx
+++ b/artfynd/A 60449-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136125881</v>
       </c>
       <c r="B2" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60449-2022 artfynd.xlsx
+++ b/artfynd/A 60449-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136125881</v>
       </c>
       <c r="B2" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60449-2022 artfynd.xlsx
+++ b/artfynd/A 60449-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136125881</v>
       </c>
       <c r="B2" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
